--- a/examples/British2American.xlsx
+++ b/examples/British2American.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CharPairs'!$A$1:$J$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'WordPairs'!$A$1:$K$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Lexicon'!$A$1:$E$88</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PunctPairs'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PunctPairs'!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>data\oeb-british.txt</t>
+          <t>data/oeb-british.txt</t>
         </is>
       </c>
     </row>
@@ -480,7 +480,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>data\oeb-american.txt</t>
+          <t>data/oeb-american.txt</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>examples\oeb-chars.csv</t>
+          <t>examples/oeb-chars.csv</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>examples\British2American.map</t>
+          <t>examples/British2American.map</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
@@ -7411,7 +7411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7419,7 +7419,7 @@
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -7472,13 +7472,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2111</v>
+        <v>2154</v>
       </c>
       <c r="D2" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.979</v>
+        <v>0.999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7503,17 +7503,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1990</v>
+        <v>2055</v>
       </c>
       <c r="D3" t="n">
-        <v>0.948</v>
+        <v>0.979</v>
       </c>
       <c r="E3" t="n">
-        <v>0.967</v>
+        <v>0.999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>bwd</t>
+          <t>both</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -7534,17 +7534,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>857</v>
+        <v>901</v>
       </c>
       <c r="D4" t="n">
-        <v>0.949</v>
+        <v>0.998</v>
       </c>
       <c r="E4" t="n">
-        <v>0.951</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>bwd</t>
+          <t>both</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -7565,120 +7565,27 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>833</v>
+        <v>897</v>
       </c>
       <c r="D5" t="n">
-        <v>0.926</v>
+        <v>0.997</v>
       </c>
       <c r="E5" t="n">
-        <v>0.884</v>
+        <v>0.952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>unreliable</t>
+          <t>both</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7141, 12723, 12758, 12758, 12862</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>‘</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>”</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>unreliable</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>24543</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>“</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>’</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>unreliable</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>24800</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>’</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>“</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>unreliable</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>26134</t>
+          <t>7141, 12723, 12758, 12758, 12806</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
